--- a/docs/spec/StrengthHub_Workout_Backend_v16.xlsx
+++ b/docs/spec/StrengthHub_Workout_Backend_v16.xlsx
@@ -1,85 +1,140 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Onboarding Questions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Coach AI Operating Rules" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Build Backlog" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Claude Code Notes" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Exercise Database" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Substitutions" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Exercise Swaps" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Summary" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Substitution Matrix" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Field Guide" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Prescription Logic" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Progression Engine" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Safety Rules" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="Screening Outcomes" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="Injury Modifications" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="Age Routing" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="Splits" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="Custom Split Rules" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="Custom Split Resolution" sheetId="19" state="visible" r:id="rId21"/>
-    <sheet name="Split Selector" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="Goal Change" sheetId="21" state="visible" r:id="rId23"/>
-    <sheet name="External Commitments" sheetId="22" state="visible" r:id="rId24"/>
-    <sheet name="Session Templates" sheetId="23" state="visible" r:id="rId25"/>
-    <sheet name="Weekly Volume" sheetId="24" state="visible" r:id="rId26"/>
-    <sheet name="Schedule Rules" sheetId="25" state="visible" r:id="rId27"/>
-    <sheet name="Exam Survival Protocol" sheetId="26" state="visible" r:id="rId28"/>
-    <sheet name="Exam Protocol Build Spec" sheetId="27" state="visible" r:id="rId29"/>
-    <sheet name="Generator Flow" sheetId="28" state="visible" r:id="rId30"/>
-    <sheet name="Data Schemas" sheetId="29" state="visible" r:id="rId31"/>
-    <sheet name="Onboarding Contract" sheetId="30" state="visible" r:id="rId32"/>
-    <sheet name="Example Week" sheetId="31" state="visible" r:id="rId33"/>
-    <sheet name="Rep Range Guide" sheetId="32" state="visible" r:id="rId34"/>
-  </sheets>
-  <definedNames>
-    <definedName function="false" hidden="true" localSheetId="15" name="_xlnm._FilterDatabase" vbProcedure="false">'Age Routing'!$A$4:$E$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Backlog'!$A$4:$H$32</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Claude Code Notes'!$A$4:$F$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="18" name="_xlnm._FilterDatabase" vbProcedure="false">'Custom Split Resolution'!$A$4:$D$18</definedName>
-    <definedName function="false" hidden="true" localSheetId="17" name="_xlnm._FilterDatabase" vbProcedure="false">'Custom Split Rules'!$A$4:$D$11</definedName>
-    <definedName function="false" hidden="true" localSheetId="28" name="_xlnm._FilterDatabase" vbProcedure="false">'Data Schemas'!$A$4:$D$11</definedName>
-    <definedName function="false" hidden="true" localSheetId="26" name="_xlnm._FilterDatabase" vbProcedure="false">'Exam Protocol Build Spec'!$A$4:$D$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="25" name="_xlnm._FilterDatabase" vbProcedure="false">'Exam Survival Protocol'!$A$4:$F$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="30" name="_xlnm._FilterDatabase" vbProcedure="false">'Example Week'!$A$4:$H$11</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Exercise Database'!$A$4:$AJ$117</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Exercise Swaps'!$A$4:$F$12</definedName>
-    <definedName function="false" hidden="true" localSheetId="21" name="_xlnm._FilterDatabase" vbProcedure="false">'External Commitments'!$A$4:$J$16</definedName>
-    <definedName function="false" hidden="true" localSheetId="27" name="_xlnm._FilterDatabase" vbProcedure="false">'Generator Flow'!$A$4:$D$18</definedName>
-    <definedName function="false" hidden="true" localSheetId="20" name="_xlnm._FilterDatabase" vbProcedure="false">'Goal Change'!$A$4:$E$13</definedName>
-    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'Injury Modifications'!$A$4:$I$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="29" name="_xlnm._FilterDatabase" vbProcedure="false">'Onboarding Contract'!$A$4:$G$35</definedName>
-    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'Prescription Logic'!$A$4:$S$24</definedName>
-    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'Progression Engine'!$A$4:$E$12</definedName>
-    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'Safety Rules'!$A$4:$G$19</definedName>
-    <definedName function="false" hidden="true" localSheetId="24" name="_xlnm._FilterDatabase" vbProcedure="false">'Schedule Rules'!$A$4:$D$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'Screening Outcomes'!$A$4:$D$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="22" name="_xlnm._FilterDatabase" vbProcedure="false">'Session Templates'!$A$4:$I$47</definedName>
-    <definedName function="false" hidden="true" localSheetId="19" name="_xlnm._FilterDatabase" vbProcedure="false">'Split Selector'!$A$4:$E$17</definedName>
-    <definedName function="false" hidden="true" localSheetId="16" name="_xlnm._FilterDatabase" vbProcedure="false">Splits!$A$4:$H$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Substitution Matrix'!$A$4:$G$114</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Substitutions!$A$4:$E$546</definedName>
-    <definedName function="false" hidden="true" localSheetId="23" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Volume'!$A$4:$E$10</definedName>
-  </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Template/>
+  <TotalTime>0</TotalTime>
+  <Application>LibreOffice/24.2.7.2$Linux_X86_64 LibreOffice_project/420$Build-2</Application>
+  <AppVersion>15.0000</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-07-08T23:27:37Z</dcterms:created>
+  <dc:creator>openpyxl</dc:creator>
+  <dc:description/>
+  <dc:language>en-US</dc:language>
+  <cp:lastModifiedBy>Zaki Sztrochlic</cp:lastModifiedBy>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-07-14T11:28:26Z</dcterms:modified>
+  <cp:revision>0</cp:revision>
+  <dc:subject/>
+  <dc:title/>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes"/>
+</file>
+
+<file path=xl\drawings\drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing25.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing27.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\drawings\drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8860" uniqueCount="3844">
   <si>
     <t xml:space="preserve">StrengthHub Online | Onboarding to Program</t>
@@ -7501,10 +7556,10 @@
     <t xml:space="preserve">SW02</t>
   </si>
   <si>
-    <t xml:space="preserve">exercise hurts (non-acute)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User says it is uncomfortable or aggravates a known area, but reports no stop symptom</t>
+    <t xml:space="preserve">exercise hurts (incl. acute sharp joint pain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User says it is uncomfortable or aggravates a known area, or reports acute sharp joint pain in a joint during the movement</t>
   </si>
   <si>
     <t xml:space="preserve">Same as SW01, and additionally skip any substitute whose Stress Regions overlap the user's affected_regions, and any sharing the flagged movement pattern. Prefer Supported=Yes and Impact=Low substitutes. Region matching is now structured (Exercise Database Stress Regions vs users.affected_regions), not inferred from names. At program-build time this is driven by the Injury Modifications sheet; mid-program pain swaps use the same region rows.</t>
@@ -7522,7 +7577,7 @@
     <t xml:space="preserve">stop symptom during exercise</t>
   </si>
   <si>
-    <t xml:space="preserve">User reports chest pain, dizziness, faintness, unusual breathlessness, palpitations, numbness or sharp joint pain</t>
+    <t xml:space="preserve">User reports chest pain, dizziness, faintness, unusual breathlessness, palpitations or numbness</t>
   </si>
   <si>
     <t xml:space="preserve">Do NOT swap and continue. Trigger Safety Rule S06: end the session, show the stop message, halt further generation until resolved or cleared. This overrides any swap request.</t>
@@ -8554,13 +8609,13 @@
     <t xml:space="preserve">S06</t>
   </si>
   <si>
-    <t xml:space="preserve">stop symptom reported: chest pain or discomfort, dizziness, fainting, unusual shortness of breath, palpitations, numbness or tingling, sharp joint pain</t>
+    <t xml:space="preserve">stop symptom reported: chest pain or discomfort, dizziness, fainting, unusual shortness of breath, palpitations, numbness or tingling</t>
   </si>
   <si>
     <t xml:space="preserve">End the session immediately. Show the stop message. Do not generate further sessions until the user confirms symptoms resolved, or professional clearance where the Screening Outcomes sheet requires it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Symptoms are never trained through. Chest pain, dizziness and fainting also prompt the user to seek medical advice.</t>
+    <t xml:space="preserve">Symptoms are never trained through. Chest pain, dizziness and fainting also prompt the user to seek medical advice. Acute sharp joint pain instead ends that exercise and routes to a pain swap (SW02) plus the Injury Modifications region rules, without freezing the whole program.</t>
   </si>
   <si>
     <t xml:space="preserve">S07</t>
@@ -8794,7 +8849,7 @@
     <t xml:space="preserve">Resolved or stable</t>
   </si>
   <si>
-    <t xml:space="preserve">Still active / flaring</t>
+    <t xml:space="preserve">Still active / flaring / unsure</t>
   </si>
   <si>
     <t xml:space="preserve">Which movements make it worse? (free text)</t>
@@ -11616,7 +11671,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
@@ -12271,115 +12326,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -12554,7 +12501,87 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Onboarding Questions" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Coach AI Operating Rules" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Build Backlog" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Claude Code Notes" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Exercise Database" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Substitutions" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Exercise Swaps" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Summary" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Substitution Matrix" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Field Guide" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Prescription Logic" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Progression Engine" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Safety Rules" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Screening Outcomes" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Injury Modifications" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Age Routing" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Splits" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Custom Split Rules" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Custom Split Resolution" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="Split Selector" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="Goal Change" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="External Commitments" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="Session Templates" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="Weekly Volume" sheetId="24" state="visible" r:id="rId26"/>
+    <sheet name="Schedule Rules" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="Exam Survival Protocol" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="Exam Protocol Build Spec" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="Generator Flow" sheetId="28" state="visible" r:id="rId30"/>
+    <sheet name="Data Schemas" sheetId="29" state="visible" r:id="rId31"/>
+    <sheet name="Onboarding Contract" sheetId="30" state="visible" r:id="rId32"/>
+    <sheet name="Example Week" sheetId="31" state="visible" r:id="rId33"/>
+    <sheet name="Rep Range Guide" sheetId="32" state="visible" r:id="rId34"/>
+  </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="15" name="_xlnm._FilterDatabase" vbProcedure="false">'Age Routing'!$A$4:$E$8</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Backlog'!$A$4:$H$32</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Claude Code Notes'!$A$4:$F$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="18" name="_xlnm._FilterDatabase" vbProcedure="false">'Custom Split Resolution'!$A$4:$D$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="17" name="_xlnm._FilterDatabase" vbProcedure="false">'Custom Split Rules'!$A$4:$D$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="28" name="_xlnm._FilterDatabase" vbProcedure="false">'Data Schemas'!$A$4:$D$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="26" name="_xlnm._FilterDatabase" vbProcedure="false">'Exam Protocol Build Spec'!$A$4:$D$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="25" name="_xlnm._FilterDatabase" vbProcedure="false">'Exam Survival Protocol'!$A$4:$F$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="30" name="_xlnm._FilterDatabase" vbProcedure="false">'Example Week'!$A$4:$H$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Exercise Database'!$A$4:$AJ$117</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Exercise Swaps'!$A$4:$F$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="21" name="_xlnm._FilterDatabase" vbProcedure="false">'External Commitments'!$A$4:$J$16</definedName>
+    <definedName function="false" hidden="true" localSheetId="27" name="_xlnm._FilterDatabase" vbProcedure="false">'Generator Flow'!$A$4:$D$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="20" name="_xlnm._FilterDatabase" vbProcedure="false">'Goal Change'!$A$4:$E$13</definedName>
+    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'Injury Modifications'!$A$4:$I$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="29" name="_xlnm._FilterDatabase" vbProcedure="false">'Onboarding Contract'!$A$4:$G$35</definedName>
+    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'Prescription Logic'!$A$4:$S$24</definedName>
+    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'Progression Engine'!$A$4:$E$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'Safety Rules'!$A$4:$G$19</definedName>
+    <definedName function="false" hidden="true" localSheetId="24" name="_xlnm._FilterDatabase" vbProcedure="false">'Schedule Rules'!$A$4:$D$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'Screening Outcomes'!$A$4:$D$8</definedName>
+    <definedName function="false" hidden="true" localSheetId="22" name="_xlnm._FilterDatabase" vbProcedure="false">'Session Templates'!$A$4:$I$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="19" name="_xlnm._FilterDatabase" vbProcedure="false">'Split Selector'!$A$4:$E$17</definedName>
+    <definedName function="false" hidden="true" localSheetId="16" name="_xlnm._FilterDatabase" vbProcedure="false">Splits!$A$4:$H$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Substitution Matrix'!$A$4:$G$114</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Substitutions!$A$4:$E$546</definedName>
+    <definedName function="false" hidden="true" localSheetId="23" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Volume'!$A$4:$E$10</definedName>
+  </definedNames>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -13292,7 +13319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -13728,7 +13755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -14769,7 +14796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -15070,7 +15097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -15476,7 +15503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -15681,7 +15708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -16044,7 +16071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -16166,7 +16193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -16492,7 +16519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -16641,7 +16668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -16887,7 +16914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17369,7 +17396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17645,7 +17672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17853,7 +17880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18304,7 +18331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -19621,7 +19648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -19876,7 +19903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -20067,7 +20094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -20319,7 +20346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -20454,7 +20481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -20701,7 +20728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -20850,7 +20877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -21652,7 +21679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -22512,7 +22539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -22881,7 +22908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -23121,7 +23148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -23314,7 +23341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -35475,7 +35502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -44743,7 +44770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -44962,7 +44989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -45570,7 +45597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
